--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -54,38 +54,62 @@
     <t>AssetType</t>
   </si>
   <si>
-    <t>Enemy_Test</t>
-  </si>
-  <si>
-    <t>Test</t>
+    <t>Spider</t>
+  </si>
+  <si>
+    <t>Enemy/Spider</t>
   </si>
   <si>
     <t>GameObject</t>
   </si>
   <si>
-    <t>Enemy_Test_01</t>
-  </si>
-  <si>
-    <t>Test_01</t>
-  </si>
-  <si>
-    <t>Exp/One</t>
-  </si>
-  <si>
-    <t>EnemyDropObject/Exp/One</t>
-  </si>
-  <si>
-    <t>Soul/One</t>
-  </si>
-  <si>
-    <t>EnemyDropObject/Soul/One</t>
+    <t>EvilMageRed</t>
+  </si>
+  <si>
+    <t>Enemy/EvilMageRed</t>
+  </si>
+  <si>
+    <t>MonsterPlant</t>
+  </si>
+  <si>
+    <t>Enemy/MonsterPlant</t>
+  </si>
+  <si>
+    <t>RatAssassin</t>
+  </si>
+  <si>
+    <t>Enemy/RatAssassin</t>
+  </si>
+  <si>
+    <t>EvilMagePuple</t>
+  </si>
+  <si>
+    <t>Enemy/EvilMagePuple</t>
+  </si>
+  <si>
+    <t>Bat</t>
+  </si>
+  <si>
+    <t>Enemy/Bat</t>
+  </si>
+  <si>
+    <t>EnemyProjectile</t>
+  </si>
+  <si>
+    <t>Enemy/Projectile_01</t>
+  </si>
+  <si>
+    <t>EnemyArea</t>
+  </si>
+  <si>
+    <t>Enemy/Area_01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -99,13 +123,18 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Carlito"/>
     </font>
   </fonts>
   <fills count="3">
@@ -122,7 +151,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border/>
     <border>
       <left style="thin">
@@ -135,6 +164,19 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="dotted">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="dotted">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="dotted">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -142,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -152,12 +194,25 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -375,7 +430,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="31.38"/>
+    <col customWidth="1" min="1" max="1" width="19.5"/>
+    <col customWidth="1" min="2" max="2" width="35.25"/>
+    <col customWidth="1" min="3" max="3" width="15.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,42 +475,92 @@
       <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="C7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="9"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -103,6 +103,18 @@
   </si>
   <si>
     <t>Enemy/Area_01</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t>EnemyDropObject/Exp/One</t>
+  </si>
+  <si>
+    <t>Soul</t>
+  </si>
+  <si>
+    <t>EnemyDropObject/Soul/One</t>
   </si>
 </sst>
 </file>
@@ -184,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -212,7 +224,12 @@
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -557,10 +574,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="9"/>
+      <c r="A12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="9"/>
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -93,12 +93,6 @@
     <t>Enemy/Bat</t>
   </si>
   <si>
-    <t>EnemyProjectile</t>
-  </si>
-  <si>
-    <t>Enemy/Projectile_01</t>
-  </si>
-  <si>
     <t>EnemyArea</t>
   </si>
   <si>
@@ -115,6 +109,24 @@
   </si>
   <si>
     <t>EnemyDropObject/Soul/One</t>
+  </si>
+  <si>
+    <t>EnemyProjectileOne</t>
+  </si>
+  <si>
+    <t>Enemy/Projectile/OrbRed</t>
+  </si>
+  <si>
+    <t>EnemyProjectileTwo</t>
+  </si>
+  <si>
+    <t>Enemy/Projectile/OrbPurple</t>
+  </si>
+  <si>
+    <t>EnemyProjectileThree</t>
+  </si>
+  <si>
+    <t>Enemy/Projectile/WindRed</t>
   </si>
 </sst>
 </file>
@@ -218,9 +230,6 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -229,6 +238,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,10 +600,32 @@
       <c r="A13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>9</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="44">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -127,6 +127,42 @@
   </si>
   <si>
     <t>Enemy/Projectile/WindRed</t>
+  </si>
+  <si>
+    <t>Scholar/ElectricArrowEffect</t>
+  </si>
+  <si>
+    <t>Scholar/FireArrowEffect</t>
+  </si>
+  <si>
+    <t>Scholar/IceArrowEffect</t>
+  </si>
+  <si>
+    <t>Scholar/MagicArrowEffect</t>
+  </si>
+  <si>
+    <t>Scholar/StoneArrowEffect</t>
+  </si>
+  <si>
+    <t>Scholar/UpgradedMagicArrowEffect</t>
+  </si>
+  <si>
+    <t>Scholar/EarthExplosionEffect</t>
+  </si>
+  <si>
+    <t>Scholar/ElectricExplosionEffect</t>
+  </si>
+  <si>
+    <t>Scholar/FireExplosionEffect</t>
+  </si>
+  <si>
+    <t>Scholar/IceExplosionEffect</t>
+  </si>
+  <si>
+    <t>Scholar/MagicExplosionEffect</t>
+  </si>
+  <si>
+    <t>Scholar/Barrier</t>
   </si>
 </sst>
 </file>
@@ -629,6 +665,138 @@
         <v>9</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>Scholar/Barrier</t>
+  </si>
+  <si>
+    <t>Hit/FireArrowHitEffect</t>
+  </si>
+  <si>
+    <t>Hit/StoneArrowHitEffect</t>
   </si>
 </sst>
 </file>
@@ -797,6 +803,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -169,6 +169,15 @@
   </si>
   <si>
     <t>Hit/StoneArrowHitEffect</t>
+  </si>
+  <si>
+    <t>Scholar/BererkSoulEffect</t>
+  </si>
+  <si>
+    <t>Scholar/BarrierExplosionEffect</t>
+  </si>
+  <si>
+    <t>PlayerProjectile</t>
   </si>
 </sst>
 </file>
@@ -825,6 +834,39 @@
         <v>9</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -177,7 +177,7 @@
     <t>Scholar/BarrierExplosionEffect</t>
   </si>
   <si>
-    <t>PlayerProjectile</t>
+    <t>ProjectileHusks</t>
   </si>
 </sst>
 </file>
@@ -510,7 +510,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.5"/>
+    <col customWidth="1" min="1" max="1" width="21.75"/>
     <col customWidth="1" min="2" max="2" width="35.25"/>
     <col customWidth="1" min="3" max="3" width="15.38"/>
   </cols>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="54">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -178,6 +178,21 @@
   </si>
   <si>
     <t>ProjectileHusks</t>
+  </si>
+  <si>
+    <t>EarthPawn_ActiveEffect</t>
+  </si>
+  <si>
+    <t>FramePawn_ActiveEffect</t>
+  </si>
+  <si>
+    <t>WaterPawn_ActiveEffect</t>
+  </si>
+  <si>
+    <t>WindBlass_Pet</t>
+  </si>
+  <si>
+    <t>WindPawn_ActiveEffect</t>
   </si>
 </sst>
 </file>
@@ -867,6 +882,61 @@
         <v>9</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="58">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -193,6 +193,18 @@
   </si>
   <si>
     <t>WindPawn_ActiveEffect</t>
+  </si>
+  <si>
+    <t>pet_fire_001</t>
+  </si>
+  <si>
+    <t>pet_water_002</t>
+  </si>
+  <si>
+    <t>pet_earth_003</t>
+  </si>
+  <si>
+    <t>pet_air_004</t>
   </si>
 </sst>
 </file>
@@ -274,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -308,6 +320,7 @@
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -937,6 +950,50 @@
         <v>9</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="60">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -205,6 +205,12 @@
   </si>
   <si>
     <t>pet_air_004</t>
+  </si>
+  <si>
+    <t>buff_water_regeneration</t>
+  </si>
+  <si>
+    <t>buff_fire_force</t>
   </si>
 </sst>
 </file>
@@ -994,6 +1000,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAssetData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
   <si>
     <t>아이디
 는 상관 없음</t>
@@ -211,6 +211,18 @@
   </si>
   <si>
     <t>buff_fire_force</t>
+  </si>
+  <si>
+    <t>Dissolve</t>
+  </si>
+  <si>
+    <t>Particle/Dissolve</t>
+  </si>
+  <si>
+    <t>DissolveRev</t>
+  </si>
+  <si>
+    <t>Particle/DissolveRev</t>
   </si>
 </sst>
 </file>
@@ -1022,6 +1034,28 @@
         <v>9</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
